--- a/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6BAE585-4F26-49A8-B120-4E9506C4D398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F18C52D-DC97-481A-BA0F-D5F1C0DC9416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{531424F7-26F2-4273-AEE6-8B41EBBF7331}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FA1871A4-CB67-4D21-8665-74E3AD566738}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -10597,7 +10597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2983E367-D75F-4CE0-9E2A-15BF4B0809AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F73060-4943-4E50-BFBD-D3FF8D2E1BD4}">
   <dimension ref="B3:L1720"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F18C52D-DC97-481A-BA0F-D5F1C0DC9416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97F4ECF1-B3A0-4EEC-9572-C70E4B321094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FA1871A4-CB67-4D21-8665-74E3AD566738}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A3FE3AD9-F5AF-4C3E-981D-2AFDCD216C4E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -10597,7 +10597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F73060-4943-4E50-BFBD-D3FF8D2E1BD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A9549BE-8EBF-410E-B772-A753D5B77AE3}">
   <dimension ref="B3:L1720"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97F4ECF1-B3A0-4EEC-9572-C70E4B321094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D652A5C9-B7B0-43B8-8482-61C477652972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A3FE3AD9-F5AF-4C3E-981D-2AFDCD216C4E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C58B714C-EAA6-4354-9AE0-B89E1502BDDB}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -10597,7 +10597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A9549BE-8EBF-410E-B772-A753D5B77AE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5FD08C0-23FE-4EEB-9112-CFE80A009494}">
   <dimension ref="B3:L1720"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D652A5C9-B7B0-43B8-8482-61C477652972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15577B43-D0A9-4E28-A979-A55A43E1D293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C58B714C-EAA6-4354-9AE0-B89E1502BDDB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3D71B993-B5A9-4B14-9423-A272EA66F22C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -10597,7 +10597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5FD08C0-23FE-4EEB-9112-CFE80A009494}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7D7BE5E-CC99-46EB-BB60-D2ABB05F9600}">
   <dimension ref="B3:L1720"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
